--- a/artfynd/A 5922-2024 artfynd.xlsx
+++ b/artfynd/A 5922-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5922-2024 artfynd.xlsx
+++ b/artfynd/A 5922-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,6 +1031,348 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115049124</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57388</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 5922, Sedingsjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>573464</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6432106</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115049048</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90283</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 5922, Sedingsjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>573184</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6432231</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>115049086</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57386</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 5922, Sedingsjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>573200</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6432201</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5922-2024 artfynd.xlsx
+++ b/artfynd/A 5922-2024 artfynd.xlsx
@@ -910,12 +910,7 @@
         <v>74116732</v>
       </c>
       <c r="B4" t="n">
-        <v>102846</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105218</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573402.714747371</v>
+        <v>573403</v>
       </c>
       <c r="R4" t="n">
-        <v>6431800.036237717</v>
+        <v>6431800</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -980,19 +975,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 5922-2024 artfynd.xlsx
+++ b/artfynd/A 5922-2024 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>74116732</v>
       </c>
       <c r="B4" t="n">
-        <v>105218</v>
+        <v>105227</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5922-2024 artfynd.xlsx
+++ b/artfynd/A 5922-2024 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>74116732</v>
       </c>
       <c r="B4" t="n">
-        <v>105227</v>
+        <v>105230</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5922-2024 artfynd.xlsx
+++ b/artfynd/A 5922-2024 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>74116732</v>
       </c>
       <c r="B4" t="n">
-        <v>105230</v>
+        <v>105258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5922-2024 artfynd.xlsx
+++ b/artfynd/A 5922-2024 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>74116732</v>
       </c>
       <c r="B4" t="n">
-        <v>105258</v>
+        <v>105264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5922-2024 artfynd.xlsx
+++ b/artfynd/A 5922-2024 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>74116732</v>
       </c>
       <c r="B4" t="n">
-        <v>105264</v>
+        <v>105271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5922-2024 artfynd.xlsx
+++ b/artfynd/A 5922-2024 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>74116732</v>
       </c>
       <c r="B4" t="n">
-        <v>105271</v>
+        <v>105275</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5922-2024 artfynd.xlsx
+++ b/artfynd/A 5922-2024 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>74116732</v>
       </c>
       <c r="B4" t="n">
-        <v>105275</v>
+        <v>105282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5922-2024 artfynd.xlsx
+++ b/artfynd/A 5922-2024 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>74116732</v>
       </c>
       <c r="B4" t="n">
-        <v>105285</v>
+        <v>105290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5922-2024 artfynd.xlsx
+++ b/artfynd/A 5922-2024 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>74116732</v>
       </c>
       <c r="B4" t="n">
-        <v>105290</v>
+        <v>105298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5922-2024 artfynd.xlsx
+++ b/artfynd/A 5922-2024 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>74116732</v>
       </c>
       <c r="B4" t="n">
-        <v>105298</v>
+        <v>105308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5922-2024 artfynd.xlsx
+++ b/artfynd/A 5922-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68422927</v>
+        <v>115049048</v>
       </c>
       <c r="B2" t="n">
-        <v>44332</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102020</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +708,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Möckelhult, Sm</t>
+          <t>A 5922, Sedingsjö, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573305.5511635548</v>
+        <v>573184</v>
       </c>
       <c r="R2" t="n">
-        <v>6432003.802565316</v>
+        <v>6432231</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-07-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,18 +765,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Helena Lager</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -794,12 +787,7 @@
         <v>68422924</v>
       </c>
       <c r="B3" t="n">
-        <v>44331</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573305.5511635548</v>
+        <v>573306</v>
       </c>
       <c r="R3" t="n">
-        <v>6432003.802565316</v>
+        <v>6432004</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +856,9 @@
           <t>2017-07-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-07-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74116732</v>
+        <v>68422927</v>
       </c>
       <c r="B4" t="n">
-        <v>105308</v>
+        <v>45046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,37 +896,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220711</v>
+        <v>102020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lungrot</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blitum bonus-henricus</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rchb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>17 Hagalund 400 m ONO t NO, Sm</t>
+          <t>Möckelhult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573403</v>
+        <v>573306</v>
       </c>
       <c r="R4" t="n">
-        <v>6431800</v>
+        <v>6432004</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,17 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1980-01-01</t>
+          <t>2017-07-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 7G6f 3108. SOM: Chenopodium bonus-henricus. LEG: Birger Danielsson</t>
+          <t>2017-07-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,40 +970,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Betesäng-bäckravin-dike</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Helena Lager</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115049124</v>
+        <v>115049086</v>
       </c>
       <c r="B5" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,26 +997,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1070,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573465</v>
+        <v>573201</v>
       </c>
       <c r="R5" t="n">
-        <v>6432105</v>
+        <v>6432201</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1132,15 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115049048</v>
+        <v>115049124</v>
       </c>
       <c r="B6" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,34 +1106,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1183,13 +1142,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573184</v>
+        <v>573465</v>
       </c>
       <c r="R6" t="n">
-        <v>6432231</v>
+        <v>6432105</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1186,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1246,65 +1204,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115049086</v>
+        <v>74116732</v>
       </c>
       <c r="B7" t="n">
-        <v>57412</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>220711</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Lungrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Blitum bonus-henricus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) Rchb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 5922, Sedingsjö, Sm</t>
+          <t>17 Hagalund 400 m ONO t NO, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573201</v>
+        <v>573403</v>
       </c>
       <c r="R7" t="n">
-        <v>6432201</v>
+        <v>6431800</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,12 +1269,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>1989-12-31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7G6f 3108. SOM: Chenopodium bonus-henricus. LEG: Birger Danielsson</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,19 +1290,28 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Betesäng-bäckravin-dike</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
